--- a/02_Glider_Design/C_results/main_text_tables.xlsx
+++ b/02_Glider_Design/C_results/main_text_tables.xlsx
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[1, 1.1]</t>
+          <t>[1, 1.074]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.06, 0.06]</t>
+          <t>[-0.02777, 0.04368]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[-2, 2]</t>
+          <t>[-0.9469, 1.57]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[0.85, 0.998]</t>
+          <t>[0.8891, 1]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[0.85, 0.993]</t>
+          <t>[0.8891, 1]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[0.85, 0.995]</t>
+          <t>[0.8891, 1]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[-2.999, 2.896]</t>
+          <t>[-2.051, 1.478]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[-2.966, 2.227]</t>
+          <t>[-1.574, 2.354]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[-2.939, 2.651]</t>
+          <t>[-2.963, 2.643]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[0.9121, 1.09]</t>
+          <t>[0.9285, 1.064]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[0.9194, 1.093]</t>
+          <t>[0.9002, 1.084]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[0.9191, 1.082]</t>
+          <t>[0.9539, 1.099]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[0.8453, 1.253]</t>
+          <t>[0.8787, 1.291]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[0.8374, 1.231]</t>
+          <t>[0.8348, 1.201]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[-0.3, 0.3]</t>
+          <t>[-0.2478, 0.284]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[-0.1725, 0.1807]</t>
+          <t>[-0.2, 0.2]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[1.018, 1.25]</t>
+          <t>[1, 1.185]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2682,15 +2682,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>not available</t>
+          <t>[0.04958, 0.9922]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Scenario uncertainty input or grouping label.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>Latent pessimistic build-quality severity variable.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Correlates mass, drag, and control effectiveness loss.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2705,12 +2709,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lhs, stress</t>
+          <t>harsh_compound, harsh_build, gusty_only, mild_compound, mild_build</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Scenario provenance tag (stress vs lhs sampling).</t>
+          <t>Original stratified robust-scenario family tag.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2730,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,7 +2770,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>nom_sink_cvar_20</t>
+          <t>nom_sink_tail_mean_k</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2859,29 +2863,31 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8035423896252482</v>
+        <v>0.722144254254269</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8509181379441859</v>
+        <v>0.7835893426482706</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8566030802229149</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>0.8007932494408697</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.039735079074368e-16</v>
+      </c>
       <c r="J2" t="n">
-        <v>0.02743333154837699</v>
+        <v>0.02582234293637892</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02467767970153566</v>
+        <v>0.01225837041169047</v>
       </c>
       <c r="L2" t="n">
-        <v>6.559576124258604</v>
+        <v>5.912015725594659</v>
       </c>
       <c r="M2" t="n">
-        <v>1.440423875741396</v>
+        <v>2.087984274405341</v>
       </c>
       <c r="N2" t="n">
-        <v>0.815082953255075</v>
+        <v>0.8241942173704815</v>
       </c>
       <c r="O2" t="n">
         <v>0.7615699665258173</v>
@@ -2924,29 +2930,31 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8035423896252482</v>
+        <v>0.722144254254269</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8509181379441859</v>
+        <v>0.7835893426482706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8566030802229149</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>0.8007932494408697</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.039735079074368e-16</v>
+      </c>
       <c r="J3" t="n">
-        <v>0.02743333154837699</v>
+        <v>0.02582234293637892</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02467767970153566</v>
+        <v>0.01225837041169047</v>
       </c>
       <c r="L3" t="n">
-        <v>6.559576124258604</v>
+        <v>5.912015725594659</v>
       </c>
       <c r="M3" t="n">
-        <v>1.440423875741396</v>
+        <v>2.087984274405341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.815082953255075</v>
+        <v>0.8241942173704815</v>
       </c>
       <c r="O3" t="n">
         <v>0.7615699665258173</v>
@@ -2989,29 +2997,31 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8035423896252482</v>
+        <v>0.722144254254269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8509181379441859</v>
+        <v>0.7835893426482706</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8566030802229149</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>0.8007932494408697</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.039735079074368e-16</v>
+      </c>
       <c r="J4" t="n">
-        <v>0.02743333154837699</v>
+        <v>0.02582234293637892</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02467767970153566</v>
+        <v>0.01225837041169047</v>
       </c>
       <c r="L4" t="n">
-        <v>6.559576124258604</v>
+        <v>5.912015725594659</v>
       </c>
       <c r="M4" t="n">
-        <v>1.440423875741396</v>
+        <v>2.087984274405341</v>
       </c>
       <c r="N4" t="n">
-        <v>0.815082953255075</v>
+        <v>0.8241942173704815</v>
       </c>
       <c r="O4" t="n">
         <v>0.7615699665258173</v>
@@ -3084,42 +3094,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lhs</t>
+          <t>harsh_compound</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.760334182882446</v>
+        <v>0.7648078796151351</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8453680304055469</v>
+        <v>0.8007932494408697</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8209706230813308</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0.7648078796151351</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.386689947160522e-17</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>harsh_build</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8413495705251999</v>
+        <v>0.7320783821112583</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8566030802229149</v>
+        <v>0.7559914076239218</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8536931917135053</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0.7320783821112583</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.950545139100166e-17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gusty_only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6641400627246555</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6641400628784476</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6641400627246555</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.222472571755847e-16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mild_compound</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7300388561113168</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7548130195179563</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7300388561113168</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.457156247633623e-16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mild_build</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7196560907089783</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7413711683834295</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7196560907089783</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.017332809056352e-17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/02_Glider_Design/C_results/main_text_tables.xlsx
+++ b/02_Glider_Design/C_results/main_text_tables.xlsx
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[1, 1.074]</t>
+          <t>[1, 1.098]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.02777, 0.04368]</t>
+          <t>[-0.05665, 0.04486]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[-0.9469, 1.57]</t>
+          <t>[-1.699, 1.893]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[0.8891, 1]</t>
+          <t>[0.8524, 1]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[0.8891, 1]</t>
+          <t>[0.8524, 1]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[0.8891, 1]</t>
+          <t>[0.8524, 1]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[-2.051, 1.478]</t>
+          <t>[-2.938, 2.69]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[-1.574, 2.354]</t>
+          <t>[-2.98, 2.82]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[-2.963, 2.643]</t>
+          <t>[-2.942, 2.665]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[0.9285, 1.064]</t>
+          <t>[0.9222, 1.098]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[0.9002, 1.084]</t>
+          <t>[0.9025, 1.057]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[0.9539, 1.099]</t>
+          <t>[0.9052, 1.099]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[0.8787, 1.291]</t>
+          <t>[0.8028, 1.275]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[0.8348, 1.201]</t>
+          <t>[0.8271, 1.296]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[-0.2478, 0.284]</t>
+          <t>[-0.2492, 0.2949]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[1, 1.185]</t>
+          <t>[1, 1.246]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[0.04958, 0.9922]</t>
+          <t>[0.0269, 0.9839]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2863,31 +2863,31 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.722144254254269</v>
+        <v>0.7212198532620753</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7835893426482706</v>
+        <v>0.8131152292092879</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8007932494408697</v>
+        <v>0.8473874312733251</v>
       </c>
       <c r="I2" t="n">
-        <v>1.039735079074368e-16</v>
+        <v>8.148278407067374e-17</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02582234293637892</v>
+        <v>0.02829097320917373</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01225837041169047</v>
+        <v>0.02019811799703457</v>
       </c>
       <c r="L2" t="n">
-        <v>5.912015725594659</v>
+        <v>6.029182010418682</v>
       </c>
       <c r="M2" t="n">
-        <v>2.087984274405341</v>
+        <v>1.970817989581318</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8241942173704815</v>
+        <v>0.8156478234142525</v>
       </c>
       <c r="O2" t="n">
         <v>0.7615699665258173</v>
@@ -2930,31 +2930,31 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.722144254254269</v>
+        <v>0.7212198532620753</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7835893426482706</v>
+        <v>0.8131152292092879</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8007932494408697</v>
+        <v>0.8473874312733251</v>
       </c>
       <c r="I3" t="n">
-        <v>1.039735079074368e-16</v>
+        <v>8.148278407067374e-17</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02582234293637892</v>
+        <v>0.02829097320917373</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01225837041169047</v>
+        <v>0.02019811799703457</v>
       </c>
       <c r="L3" t="n">
-        <v>5.912015725594659</v>
+        <v>6.029182010418682</v>
       </c>
       <c r="M3" t="n">
-        <v>2.087984274405341</v>
+        <v>1.970817989581318</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8241942173704815</v>
+        <v>0.8156478234142525</v>
       </c>
       <c r="O3" t="n">
         <v>0.7615699665258173</v>
@@ -2997,31 +2997,31 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.722144254254269</v>
+        <v>0.7212198532620753</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7835893426482706</v>
+        <v>0.8131152292092879</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8007932494408697</v>
+        <v>0.8473874312733251</v>
       </c>
       <c r="I4" t="n">
-        <v>1.039735079074368e-16</v>
+        <v>8.148278407067374e-17</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02582234293637892</v>
+        <v>0.02829097320917373</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01225837041169047</v>
+        <v>0.02019811799703457</v>
       </c>
       <c r="L4" t="n">
-        <v>5.912015725594659</v>
+        <v>6.029182010418682</v>
       </c>
       <c r="M4" t="n">
-        <v>2.087984274405341</v>
+        <v>1.970817989581318</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8241942173704815</v>
+        <v>0.8156478234142525</v>
       </c>
       <c r="O4" t="n">
         <v>0.7615699665258173</v>
@@ -3101,16 +3101,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7648078796151351</v>
+        <v>0.7851282816551723</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8007932494408697</v>
+        <v>0.8473874312733251</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7648078796151351</v>
+        <v>0.8364830112658391</v>
       </c>
       <c r="F10" t="n">
-        <v>7.386689947160522e-17</v>
+        <v>7.829303585837255e-17</v>
       </c>
     </row>
     <row r="11">
@@ -3123,16 +3123,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7320783821112583</v>
+        <v>0.7556669225157714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7559914076239218</v>
+        <v>0.8214872114936375</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7320783821112583</v>
+        <v>0.7933410038400295</v>
       </c>
       <c r="F11" t="n">
-        <v>9.950545139100166e-17</v>
+        <v>8.15813631655874e-17</v>
       </c>
     </row>
     <row r="12">
@@ -3145,16 +3145,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6641400627246555</v>
+        <v>0.6641400639820511</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6641400628784476</v>
+        <v>0.6641400716972593</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6641400627246555</v>
+        <v>0.6641400657601114</v>
       </c>
       <c r="F12" t="n">
-        <v>1.222472571755847e-16</v>
+        <v>1.025764922902452e-16</v>
       </c>
     </row>
     <row r="13">
@@ -3167,16 +3167,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7300388561113168</v>
+        <v>0.688070385554021</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7548130195179563</v>
+        <v>0.737146896441633</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7300388561113168</v>
+        <v>0.7100387396320821</v>
       </c>
       <c r="F13" t="n">
-        <v>1.457156247633623e-16</v>
+        <v>7.015878333351152e-17</v>
       </c>
     </row>
     <row r="14">
@@ -3189,16 +3189,16 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7196560907089783</v>
+        <v>0.7130936126033608</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7413711683834295</v>
+        <v>0.7474609577009502</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7196560907089783</v>
+        <v>0.7382178203510006</v>
       </c>
       <c r="F14" t="n">
-        <v>5.017332809056352e-17</v>
+        <v>7.048198755891459e-17</v>
       </c>
     </row>
   </sheetData>

--- a/02_Glider_Design/C_results/main_text_tables.xlsx
+++ b/02_Glider_Design/C_results/main_text_tables.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ineq constraint; margin=-9.957e-09</t>
+          <t>ineq constraint; margin=-9.954e-09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ineq constraint; margin=-9.924e-09</t>
+          <t>ineq constraint; margin=-9.908e-09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[1, 1.098]</t>
+          <t>[1.028, 1.028]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.05665, 0.04486]</t>
+          <t>[-0.04539, -0.04539]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[-1.699, 1.893]</t>
+          <t>[0.09043, 0.09043]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[0.8524, 1]</t>
+          <t>[0.958, 0.958]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[0.8524, 1]</t>
+          <t>[0.958, 0.958]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[0.8524, 1]</t>
+          <t>[0.958, 0.958]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[-2.938, 2.69]</t>
+          <t>[-0.545, -0.545]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[-2.98, 2.82]</t>
+          <t>[-2.57, -2.57]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[-2.942, 2.665]</t>
+          <t>[-2.406, -2.406]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[0.9222, 1.098]</t>
+          <t>[1.097, 1.097]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[0.9025, 1.057]</t>
+          <t>[1.039, 1.039]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[0.9052, 1.099]</t>
+          <t>[0.9897, 0.9897]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[0.8028, 1.275]</t>
+          <t>[1.12, 1.12]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[0.8271, 1.296]</t>
+          <t>[0.9352, 0.9352]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[-0.2492, 0.2949]</t>
+          <t>[-0.1189, -0.1189]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[-0.2, 0.2]</t>
+          <t>[-0.09122, -0.09122]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[1, 1.246]</t>
+          <t>[1.07, 1.07]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[0.0269, 0.9839]</t>
+          <t>[0.2801, 0.2801]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>harsh_compound, harsh_build, gusty_only, mild_compound, mild_build</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2857,58 +2857,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.166267395045595</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7212198532620753</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8473874312733251</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="I2" t="n">
-        <v>8.148278407067374e-17</v>
+        <v>1.4285713188503e-17</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02829097320917373</v>
+        <v>0.02553436812845662</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02019811799703457</v>
+        <v>0.01588149296636211</v>
       </c>
       <c r="L2" t="n">
-        <v>6.029182010418682</v>
+        <v>4.886000453231397</v>
       </c>
       <c r="M2" t="n">
-        <v>1.970817989581318</v>
+        <v>3.113999546768603</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8156478234142525</v>
+        <v>0.8402748655179237</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7615699665258173</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1646396705960972</v>
+        <v>0.1646396706102183</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1175251467514151</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1000000099235376</v>
+        <v>0.1000000099082708</v>
       </c>
       <c r="T2" t="n">
-        <v>9.696954368839226</v>
+        <v>9.696954368874374</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537634592</v>
       </c>
     </row>
     <row r="3">
@@ -2924,58 +2924,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.166267395045595</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7212198532620753</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8473874312733251</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="I3" t="n">
-        <v>8.148278407067374e-17</v>
+        <v>1.4285713188503e-17</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02829097320917373</v>
+        <v>0.02553436812845662</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02019811799703457</v>
+        <v>0.01588149296636211</v>
       </c>
       <c r="L3" t="n">
-        <v>6.029182010418682</v>
+        <v>4.886000453231397</v>
       </c>
       <c r="M3" t="n">
-        <v>1.970817989581318</v>
+        <v>3.113999546768603</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8156478234142525</v>
+        <v>0.8402748655179237</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7615699665258173</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1646396705960972</v>
+        <v>0.1646396706102183</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1175251467514151</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1000000099235376</v>
+        <v>0.1000000099082708</v>
       </c>
       <c r="T3" t="n">
-        <v>9.696954368839226</v>
+        <v>9.696954368874374</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537634592</v>
       </c>
     </row>
     <row r="4">
@@ -2991,58 +2991,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.166267395045595</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7212198532620753</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8473874312733251</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="I4" t="n">
-        <v>8.148278407067374e-17</v>
+        <v>1.4285713188503e-17</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02829097320917373</v>
+        <v>0.02553436812845662</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02019811799703457</v>
+        <v>0.01588149296636211</v>
       </c>
       <c r="L4" t="n">
-        <v>6.029182010418682</v>
+        <v>4.886000453231397</v>
       </c>
       <c r="M4" t="n">
-        <v>1.970817989581318</v>
+        <v>3.113999546768603</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8156478234142525</v>
+        <v>0.8402748655179237</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7615699665258173</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1646396705960972</v>
+        <v>0.1646396706102183</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5639716232510613</v>
+        <v>0.5639716234248189</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1175251467514151</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1000000099235376</v>
+        <v>0.1000000099082708</v>
       </c>
       <c r="T4" t="n">
-        <v>9.696954368839226</v>
+        <v>9.696954368874374</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6703135537658776</v>
+        <v>0.6703135537634592</v>
       </c>
     </row>
     <row r="7">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>sink_tail_mean_k</t>
+          <t>nom_sink_tail_mean_k</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -3094,111 +3094,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>harsh_compound</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7851282816551723</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8473874312733251</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8364830112658391</v>
+        <v>0.7162069461328315</v>
       </c>
       <c r="F10" t="n">
-        <v>7.829303585837255e-17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>harsh_build</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7556669225157714</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.8214872114936375</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.7933410038400295</v>
-      </c>
-      <c r="F11" t="n">
-        <v>8.15813631655874e-17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>gusty_only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.6641400639820511</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.6641400716972593</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6641400657601114</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.025764922902452e-16</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>mild_compound</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.688070385554021</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.737146896441633</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.7100387396320821</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7.015878333351152e-17</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>mild_build</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.7130936126033608</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.7474609577009502</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.7382178203510006</v>
-      </c>
-      <c r="F14" t="n">
-        <v>7.048198755891459e-17</v>
+        <v>1.4285713188503e-17</v>
       </c>
     </row>
   </sheetData>

--- a/02_Glider_Design/C_results/main_text_tables.xlsx
+++ b/02_Glider_Design/C_results/main_text_tables.xlsx
@@ -2734,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2750,95 +2750,150 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>robust_rank</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>selected_flag</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>objective</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_success</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>nom_success_rate</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>nom_failure_rate</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>nom_sink_mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>nom_sink_tail_mean_k</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>nom_sink_p95</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>nom_sink_worst</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>nom_resid_rmse_success_only</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>nom_roll_tau_p95</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>nom_roll_tau_worst</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_e_util_p95</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>nom_delta_e_util_worst</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>nom_alpha_worst</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>nom_alpha_p95</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>nom_alpha_margin_p05</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>nom_alpha_margin_worst</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>nom_cl_margin_p05</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>nom_cl_margin_worst</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>nom_wing_deflection_over_allow_worst</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>nom_htail_deflection_over_allow_worst</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>wing_span_m</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>wing_chord_m</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>boom_length_m</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mass_total_kg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>static_margin</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>L_over_D</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>sink_rate_mps</t>
         </is>
@@ -2853,61 +2908,70 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="b">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>2.166267395066876</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="I2" t="n">
+      <c r="N2" t="n">
         <v>1.4285713188503e-17</v>
       </c>
-      <c r="J2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>0.02553436812845662</v>
       </c>
-      <c r="K2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
         <v>0.01588149296636211</v>
       </c>
-      <c r="L2" t="n">
-        <v>4.886000453231397</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
         <v>3.113999546768603</v>
       </c>
-      <c r="N2" t="n">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
         <v>0.8402748655179237</v>
       </c>
-      <c r="O2" t="n">
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
         <v>0.761569966525819</v>
       </c>
-      <c r="P2" t="n">
+      <c r="AA2" t="n">
         <v>0.1646396706102183</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AB2" t="n">
         <v>0.5639716234248189</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AC2" t="n">
         <v>0.1175251467546148</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AD2" t="n">
         <v>0.1000000099082708</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AE2" t="n">
         <v>9.696954368874374</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AF2" t="n">
         <v>0.6703135537634592</v>
       </c>
     </row>
@@ -2920,61 +2984,70 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="b">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="b">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2.166267395066876</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="I3" t="n">
+      <c r="N3" t="n">
         <v>1.4285713188503e-17</v>
       </c>
-      <c r="J3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0.02553436812845662</v>
       </c>
-      <c r="K3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
         <v>0.01588149296636211</v>
       </c>
-      <c r="L3" t="n">
-        <v>4.886000453231397</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
         <v>3.113999546768603</v>
       </c>
-      <c r="N3" t="n">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
         <v>0.8402748655179237</v>
       </c>
-      <c r="O3" t="n">
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
         <v>0.761569966525819</v>
       </c>
-      <c r="P3" t="n">
+      <c r="AA3" t="n">
         <v>0.1646396706102183</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AB3" t="n">
         <v>0.5639716234248189</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AC3" t="n">
         <v>0.1175251467546148</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AD3" t="n">
         <v>0.1000000099082708</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AE3" t="n">
         <v>9.696954368874374</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AF3" t="n">
         <v>0.6703135537634592</v>
       </c>
     </row>
@@ -2987,61 +3060,70 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2.166267395066876</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="G4" t="n">
+      <c r="K4" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="H4" t="n">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="I4" t="n">
+      <c r="N4" t="n">
         <v>1.4285713188503e-17</v>
       </c>
-      <c r="J4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>0.02553436812845662</v>
       </c>
-      <c r="K4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
         <v>0.01588149296636211</v>
       </c>
-      <c r="L4" t="n">
-        <v>4.886000453231397</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>3.113999546768603</v>
       </c>
-      <c r="N4" t="n">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
         <v>0.8402748655179237</v>
       </c>
-      <c r="O4" t="n">
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
         <v>0.761569966525819</v>
       </c>
-      <c r="P4" t="n">
+      <c r="AA4" t="n">
         <v>0.1646396706102183</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="AB4" t="n">
         <v>0.5639716234248189</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AC4" t="n">
         <v>0.1175251467546148</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AD4" t="n">
         <v>0.1000000099082708</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AE4" t="n">
         <v>9.696954368874374</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AF4" t="n">
         <v>0.6703135537634592</v>
       </c>
     </row>
@@ -3067,27 +3149,57 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
+          <t>n_fail</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>failure_rate</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
           <t>success_rate</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>sink_mean</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>sink_p95</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>sink_worst</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>nom_sink_tail_mean_k</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>nom_resid_rmse_success_only</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>nom_alpha_margin_worst</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>nom_cl_margin_worst</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>nom_delta_e_util_worst</t>
         </is>
       </c>
     </row>
@@ -3097,21 +3209,27 @@
           <t>mixed</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
         <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7162069461328315</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.7162069461328315</v>
       </c>
       <c r="E10" t="n">
         <v>0.7162069461328315</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0.7162069461328315</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7162069461328315</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.4285713188503e-17</v>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/02_Glider_Design/C_results/main_text_tables.xlsx
+++ b/02_Glider_Design/C_results/main_text_tables.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ineq constraint; margin=-9.989e-09</t>
+          <t>ineq constraint; margin=-9.975e-09</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ineq constraint; margin=-9.954e-09</t>
+          <t>ineq constraint; margin=-9.847e-09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ineq constraint; margin=-9.908e-09</t>
+          <t>ineq constraint; margin=-9.774e-09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ineq constraint; margin=-9.976e-09</t>
+          <t>ineq constraint; margin=-9.943e-09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[1.028, 1.028]</t>
+          <t>[1, 1.099]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.04539, -0.04539]</t>
+          <t>[-0.05916, 0.05887]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[0.09043, 0.09043]</t>
+          <t>[-1.93, 1.979]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[0.958, 0.958]</t>
+          <t>[0.851, 1]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[0.958, 0.958]</t>
+          <t>[0.851, 1]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[0.958, 0.958]</t>
+          <t>[0.851, 1]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[-0.545, -0.545]</t>
+          <t>[-2.963, 2.91]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[-2.57, -2.57]</t>
+          <t>[-2.957, 2.958]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[-2.406, -2.406]</t>
+          <t>[-2.896, 2.97]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[1.097, 1.097]</t>
+          <t>[0.9027, 1.095]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[1.039, 1.039]</t>
+          <t>[0.9002, 1.1]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[0.9897, 0.9897]</t>
+          <t>[0.9019, 1.098]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[1.12, 1.12]</t>
+          <t>[0.8111, 1.297]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[0.9352, 0.9352]</t>
+          <t>[0.8189, 1.294]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[-0.1189, -0.1189]</t>
+          <t>[-0.2963, 0.2835]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[-0.09122, -0.09122]</t>
+          <t>[-0.2, 0.2]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[1.07, 1.07]</t>
+          <t>[1, 1.248]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[0.2801, 0.2801]</t>
+          <t>[0.006604, 0.9933]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>harsh_compound, harsh_build, gusty_only, mild_compound, mild_build</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2908,71 +2908,95 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2.166267395066876</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+        <v>2.166267394925852</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.7198949840627062</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7162069461328315</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>0.8092788230214379</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8241554920088505</v>
+      </c>
       <c r="M2" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.8516007402092221</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4285713188503e-17</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>1.036883614947767e-16</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02606001747705105</v>
+      </c>
       <c r="P2" t="n">
-        <v>0.02553436812845662</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>0.02685308242023638</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01809588365504656</v>
+      </c>
       <c r="R2" t="n">
-        <v>0.01588149296636211</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>0.02234294046135802</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.368646570955923</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.631353429044077</v>
+      </c>
       <c r="U2" t="n">
-        <v>3.113999546768603</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>0.2281261864201518</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8199767777234717</v>
+      </c>
       <c r="W2" t="n">
-        <v>0.8402748655179237</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>0.8153179752247507</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3082379254904147</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.1537292411057699</v>
+      </c>
       <c r="Z2" t="n">
-        <v>0.761569966525819</v>
+        <v>0.7615699665201038</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1646396706102183</v>
+        <v>0.1646396705205474</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5639716234248189</v>
+        <v>0.5639716216232333</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1175251467546148</v>
+        <v>0.117525146731925</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1000000099082708</v>
+        <v>0.1000000097739628</v>
       </c>
       <c r="AE2" t="n">
-        <v>9.696954368874374</v>
+        <v>9.696954368082954</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6703135537634592</v>
+        <v>0.6703135538267228</v>
       </c>
     </row>
     <row r="3">
@@ -2984,71 +3008,95 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2.166267395066876</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+        <v>2.166267394925852</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
       <c r="J3" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.7198949840627062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7162069461328315</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>0.8092788230214379</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8241554920088505</v>
+      </c>
       <c r="M3" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.8516007402092221</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4285713188503e-17</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>1.036883614947767e-16</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02606001747705105</v>
+      </c>
       <c r="P3" t="n">
-        <v>0.02553436812845662</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>0.02685308242023638</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.01809588365504656</v>
+      </c>
       <c r="R3" t="n">
-        <v>0.01588149296636211</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+        <v>0.02234294046135802</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6.368646570955923</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.631353429044077</v>
+      </c>
       <c r="U3" t="n">
-        <v>3.113999546768603</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>0.2281261864201518</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8199767777234717</v>
+      </c>
       <c r="W3" t="n">
-        <v>0.8402748655179237</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+        <v>0.8153179752247507</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3082379254904147</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1537292411057699</v>
+      </c>
       <c r="Z3" t="n">
-        <v>0.761569966525819</v>
+        <v>0.7615699665201038</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1646396706102183</v>
+        <v>0.1646396705205474</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5639716234248189</v>
+        <v>0.5639716216232333</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1175251467546148</v>
+        <v>0.117525146731925</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1000000099082708</v>
+        <v>0.1000000097739628</v>
       </c>
       <c r="AE3" t="n">
-        <v>9.696954368874374</v>
+        <v>9.696954368082954</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6703135537634592</v>
+        <v>0.6703135538267228</v>
       </c>
     </row>
     <row r="4">
@@ -3060,71 +3108,95 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2.166267395066876</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>2.166267394925852</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.7198949840627062</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7162069461328315</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>0.8092788230214379</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8241554920088505</v>
+      </c>
       <c r="M4" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.8516007402092221</v>
       </c>
       <c r="N4" t="n">
-        <v>1.4285713188503e-17</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>1.036883614947767e-16</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02606001747705105</v>
+      </c>
       <c r="P4" t="n">
-        <v>0.02553436812845662</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>0.02685308242023638</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01809588365504656</v>
+      </c>
       <c r="R4" t="n">
-        <v>0.01588149296636211</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+        <v>0.02234294046135802</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6.368646570955923</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.631353429044077</v>
+      </c>
       <c r="U4" t="n">
-        <v>3.113999546768603</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>0.2281261864201518</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8199767777234717</v>
+      </c>
       <c r="W4" t="n">
-        <v>0.8402748655179237</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+        <v>0.8153179752247507</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3082379254904147</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.1537292411057699</v>
+      </c>
       <c r="Z4" t="n">
-        <v>0.761569966525819</v>
+        <v>0.7615699665201038</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1646396706102183</v>
+        <v>0.1646396705205474</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5639716234248189</v>
+        <v>0.5639716216232333</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1175251467546148</v>
+        <v>0.117525146731925</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1000000099082708</v>
+        <v>0.1000000097739628</v>
       </c>
       <c r="AE4" t="n">
-        <v>9.696954368874374</v>
+        <v>9.696954368082954</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.6703135537634592</v>
+        <v>0.6703135538267228</v>
       </c>
     </row>
     <row r="7">
@@ -3206,30 +3278,202 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+          <t>harsh_compound</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7162069461328315</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0.7540318657782118</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8320968074142782</v>
+      </c>
       <c r="G10" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.8463133131039565</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7162069461328315</v>
+        <v>0.832358623364495</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4285713188503e-17</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>7.86307523223378e-17</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2281261864201518</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.816598330646168</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02234294046135802</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>harsh_build</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7627282978542079</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8438668844717189</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8516007402092221</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8317739114031938</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.471631644673092e-16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.093865078126169</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8153179752247507</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0180735927185613</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gusty_only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6641400643173269</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6641400691295222</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6641400744223981</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6641400696431005</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8.617327938735885e-17</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.661557748467938</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8500754101960935</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0009868962076551972</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mild_compound</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7048773345014447</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7482473156368605</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7532653825809689</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7457886746104015</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.125426252593924e-17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.106604890662146</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8329256900963731</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.00940252492017157</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mild_build</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7136973578623396</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.74845387107978</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7533834146125964</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7461816819631687</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.0081376320237e-16</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.36279520963209</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8331326438555489</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01091170243156747</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
